--- a/Databases/Database3/Output/2015/db3_2015_extracted.xlsx
+++ b/Databases/Database3/Output/2015/db3_2015_extracted.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>UL:S; UR:FW; LR:OB</t>
+          <t>UL:S; LL:-; UR:FW; LR:OB</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BO; LR:WB</t>
+          <t>UL:FG; LL:BO; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>UL:O; LL:O/Y; UR:S</t>
+          <t>UL:O; LL:O/Y; UR:S; LR:-</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -886,7 +886,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UL:O; LL:Lb; UR:S</t>
+          <t>UL:O; LL:Lb; UR:S; LR:-</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9:17-10:57</t>
+          <t>09:17 - 10:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9:00-11:45am</t>
+          <t>09:00 - 11:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1295,7 +1295,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LR:A/B</t>
+          <t>UL:-; LL:-; UR:-; LR:A/B</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>LL:G; UR:FG; LR:GK</t>
+          <t>UL:-; LL:G; UR:FG; LR:GK</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BB; LR:Y</t>
+          <t>UL:FG; LL:BB; UR:-; LR:Y</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>LL:YO; UR:FG; LR:WY</t>
+          <t>UL:-; LL:YO; UR:FG; LR:WY</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>UL:FY; UR:S</t>
+          <t>UL:FY; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1130-1230</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1130-1230</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:34-2;45</t>
+          <t>12:34 - 02:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2488,7 +2488,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>UL:O; UR:S; LR:Lg/O/Lg</t>
+          <t>UL:O; LL:-; UR:S; LR:Lg/O/Lg</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BK; LR:GY</t>
+          <t>UL:FG; LL:BK; UR:-; LR:GY</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>UL:G; LL:KK; UR:FG</t>
+          <t>UL:G; LL:KK; UR:FG; LR:-</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>UL:FG; LL:YB; LR:WR</t>
+          <t>UL:FG; LL:YB; UR:-; LR:WR</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:Yf; UR:S</t>
+          <t>Orientation:Horizontal; UL:Yf; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>UL:Gf; LL:OO; LR:WB</t>
+          <t>UL:Gf; LL:OO; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>UL:Of; LL:RR; LR:bS</t>
+          <t>UL:Of; LL:RR; UR:-; LR:bS</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3381,7 +3381,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>UL:R; LL:G/B; LR:Y/G/R</t>
+          <t>UL:R; LL:G/B; UR:-; LR:Y/G/R</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9:40 am - 12:10 pm</t>
+          <t>09:40 - 12:10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7:30 - 9:00 am</t>
+          <t>07:30 - 09:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3700,7 +3700,11 @@
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -3713,7 +3717,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3751,7 +3755,11 @@
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -3764,7 +3772,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3802,7 +3810,11 @@
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -3815,7 +3827,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3862,7 +3874,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3900,7 +3912,11 @@
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -3913,7 +3929,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3951,7 +3967,11 @@
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -3964,7 +3984,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4011,7 +4031,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4049,7 +4069,11 @@
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -4062,7 +4086,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4100,7 +4124,11 @@
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -4113,7 +4141,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4151,7 +4179,11 @@
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -4164,7 +4196,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4202,7 +4234,11 @@
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -4215,7 +4251,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4262,7 +4298,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4315,7 +4351,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4360,7 +4396,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4417,7 +4453,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4472,7 +4508,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4525,7 +4561,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4570,7 +4606,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4611,7 +4647,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4652,7 +4688,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4694,7 +4730,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>UL:S; LL:Lb or Lg; LR:0</t>
+          <t>UL:S; LL:Lb or Lg; UR:-; LR:0</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -4709,7 +4745,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4750,7 +4786,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4791,7 +4827,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4836,7 +4872,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4881,7 +4917,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4922,7 +4958,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4964,7 +5000,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:B/B; LR:Y/W</t>
+          <t>UL:F(G); LL:B/B; UR:-; LR:Y/W</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -4979,7 +5015,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5021,7 +5057,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:K; UR:G</t>
+          <t>UL:F(G); LL:K; UR:G; LR:-</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5036,7 +5072,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5081,7 +5117,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5123,7 +5159,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Orientation:horizontal; UL:S; UR:F(A)</t>
+          <t>Orientation:horizontal; UL:S; LL:-; UR:F(A); LR:-</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -5134,7 +5170,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5175,7 +5211,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>09:12-10:35</t>
+          <t>09:12 - 10:35</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5220,7 +5256,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5277,7 +5313,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5319,7 +5355,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>UL:F(W); UR:S</t>
+          <t>UL:F(W); LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -5334,7 +5370,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5376,7 +5412,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:W/O; UR:Y</t>
+          <t>UL:F(G); LL:W/O; UR:Y; LR:-</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -5391,7 +5427,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5433,7 +5469,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>LL:W/W; UR:F(G); LR:O/Y</t>
+          <t>UL:-; LL:W/W; UR:F(G); LR:O/Y</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -5448,7 +5484,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5505,7 +5541,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5550,7 +5586,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5595,7 +5631,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>10:30 AM-12:30 PM</t>
+          <t>10:30 - 12:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5636,7 +5672,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5689,7 +5725,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5742,7 +5778,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5787,7 +5823,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5832,7 +5868,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5919,7 +5955,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; UR:S</t>
+          <t>Orientation:Horizontal; UL:FY; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -6029,7 +6065,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BG; LR:WB</t>
+          <t>UL:FG; LL:BG; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -6086,7 +6122,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; LL:GB; LR:GP</t>
+          <t>Orientation:Horizontal; UL:FY; LL:GB; UR:-; LR:GP</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -6462,7 +6498,7 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>UL:S; LL:BO</t>
+          <t>UL:S; LL:BO; UR:-; LR:-</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -6620,7 +6656,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>07:45 / 17:30</t>
+          <t>07:45 - 17:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6665,7 +6701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>11:44 - 01:21</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6706,7 +6742,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>11:44 - 01:21</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
